--- a/Data/Set_Covering_USA_200k_Model.xlsx
+++ b/Data/Set_Covering_USA_200k_Model.xlsx
@@ -1,49 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Model" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Cities" sheetId="2" state="visible" r:id="rId5"/>
+    <sheet name="Model" sheetId="1" r:id="rId10"/>
+    <sheet name="Cities" sheetId="2" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_adj" vbProcedure="false">Model!$B$133:$DY$133</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_cvg" vbProcedure="false">0.0001</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_drv" vbProcedure="false">1</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_eng" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_est" vbProcedure="false">1</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_itr" vbProcedure="false">2147483647</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_lhs1" vbProcedure="false">Model!$DZ$4:$DZ$131</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_lhs2" vbProcedure="false">Model!$B$133:$DY$133</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_lin" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_mip" vbProcedure="false">2147483647</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_mni" vbProcedure="false">30</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_mrt" vbProcedure="false">0.075</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_msl" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_ncr" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_neg" vbProcedure="false">1</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_nod" vbProcedure="false">2147483647</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_num" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_nwt" vbProcedure="false">1</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_opt" vbProcedure="false">Model!$B$136</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_pre" vbProcedure="false">1</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_rel1" vbProcedure="false">3</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_rel2" vbProcedure="false">5</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_rhs1" vbProcedure="false">Model!$EB$4:$EB$131</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_rhs2" vbProcedure="false">binary</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_rlx" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_rsd" vbProcedure="false">0</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_scl" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_show" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_sol" vbProcedure="false">2147483647</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_ssz" vbProcedure="false">100</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_tim" vbProcedure="false">2147483647</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_tol" vbProcedure="false">0</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_typ" vbProcedure="false">2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="solver_ver" vbProcedure="false">3</definedName>
+    <definedName name="solver_adj" hidden="true" localSheetId="0">Model!$B$133:$DY$133</definedName>
+    <definedName name="solver_cvg" hidden="true" localSheetId="0">0.0001</definedName>
+    <definedName name="solver_drv" hidden="true" localSheetId="0">1</definedName>
+    <definedName name="solver_eng" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_est" hidden="true" localSheetId="0">1</definedName>
+    <definedName name="solver_itr" hidden="true" localSheetId="0">2147483647</definedName>
+    <definedName name="solver_lhs1" hidden="true" localSheetId="0">Model!$DZ$4:$DZ$131</definedName>
+    <definedName name="solver_lhs2" hidden="true" localSheetId="0">Model!$B$133:$DY$133</definedName>
+    <definedName name="solver_lin" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_mip" hidden="true" localSheetId="0">2147483647</definedName>
+    <definedName name="solver_mni" hidden="true" localSheetId="0">30</definedName>
+    <definedName name="solver_mrt" hidden="true" localSheetId="0">0.075</definedName>
+    <definedName name="solver_msl" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_ncr" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_neg" hidden="true" localSheetId="0">1</definedName>
+    <definedName name="solver_nod" hidden="true" localSheetId="0">2147483647</definedName>
+    <definedName name="solver_num" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_nwt" hidden="true" localSheetId="0">1</definedName>
+    <definedName name="solver_opt" hidden="true" localSheetId="0">Model!$B$136</definedName>
+    <definedName name="solver_pre" hidden="true" localSheetId="0">1</definedName>
+    <definedName name="solver_rel1" hidden="true" localSheetId="0">3</definedName>
+    <definedName name="solver_rel2" hidden="true" localSheetId="0">5</definedName>
+    <definedName name="solver_rhs1" hidden="true" localSheetId="0">Model!$EB$4:$EB$131</definedName>
+    <definedName name="solver_rhs2" hidden="true" localSheetId="0">binary</definedName>
+    <definedName name="solver_rlx" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_rsd" hidden="true" localSheetId="0">0</definedName>
+    <definedName name="solver_scl" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_show" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_sol" hidden="true" localSheetId="0">2147483647</definedName>
+    <definedName name="solver_ssz" hidden="true" localSheetId="0">100</definedName>
+    <definedName name="solver_tim" hidden="true" localSheetId="0">2147483647</definedName>
+    <definedName name="solver_tol" hidden="true" localSheetId="0">0</definedName>
+    <definedName name="solver_typ" hidden="true" localSheetId="0">2</definedName>
+    <definedName name="solver_ver" hidden="true" localSheetId="0">3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="true"/>
 </workbook>
@@ -2167,9 +2166,9 @@
   <dimension ref="A1:EB144"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="26"/>
-    <col customWidth="true" max="129" min="2" width="5"/>
-    <col customWidth="true" max="132" min="130" width="11"/>
+    <col min="1" max="1" width="26" customWidth="true"/>
+    <col min="2" max="129" width="5" customWidth="true"/>
+    <col min="130" max="132" width="11" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -54472,11 +54471,11 @@
   <dimension ref="A1:I131"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="6"/>
-    <col customWidth="true" max="2" min="2" width="18"/>
-    <col customWidth="true" max="3" min="3" width="7"/>
-    <col customWidth="true" max="8" min="4" width="17"/>
-    <col customWidth="true" max="9" min="9" width="46"/>
+    <col min="1" max="1" width="6" customWidth="true"/>
+    <col min="2" max="2" width="18" customWidth="true"/>
+    <col min="3" max="3" width="7" customWidth="true"/>
+    <col min="4" max="8" width="17" customWidth="true"/>
+    <col min="9" max="9" width="46" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
